--- a/Entregables/matriz-rol-Responsabilidad-17-09.xlsx
+++ b/Entregables/matriz-rol-Responsabilidad-17-09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbautneduar-my.sharepoint.com/personal/jomansilla_frba_utn_edu_ar/Documents/04-Cuarto-Año-2026/Administracion-De-Sistemas-De-Información/TPA/Entregables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="362" documentId="13_ncr:1_{37DFC270-423E-4D5F-9989-95A508490E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E22862E3-308F-49D7-8F3D-01FA710D42F0}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="13_ncr:1_{37DFC270-423E-4D5F-9989-95A508490E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{737B4037-0CB0-4771-B177-B7A6BDC3FC75}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz de Roles" sheetId="1" r:id="rId1"/>
@@ -117,12 +117,6 @@
     <t>Senior (5+ años)</t>
   </si>
   <si>
-    <t>• PMBOK / metodologías ágiles (Scrum/Kanban)
-• Gestión de riesgos y cronograma
-• MS Project / Jira
-• Presupuestación y control de costos</t>
-  </si>
-  <si>
     <t>• Liderazgo y toma de decisiones
 • Comunicación efectiva con stakeholders
 • Gestión del cambio
@@ -819,6 +813,10 @@
   </si>
   <si>
     <t>Proyecto:</t>
+  </si>
+  <si>
+    <t>• Gestión de riesgos y cronograma
+• Presupuestación y control de costos</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1280,80 +1278,79 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1669,7 +1666,7 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AD75"/>
+  <dimension ref="A1:R75"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.42578125" customWidth="1"/>
@@ -1677,51 +1674,51 @@
     <col min="3" max="14" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:18" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+    </row>
+    <row r="2" spans="1:18" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-    </row>
-    <row r="2" spans="1:30" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
-        <v>221</v>
-      </c>
-      <c r="B2" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-    </row>
-    <row r="3" spans="1:30" ht="33.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
+    </row>
+    <row r="3" spans="1:18" ht="33.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1</v>
@@ -1751,43 +1748,31 @@
         <v>9</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="R3" s="53"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
-      <c r="AA3" s="50"/>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-    </row>
-    <row r="4" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="R3" s="28"/>
+    </row>
+    <row r="4" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G4" s="21"/>
       <c r="H4" s="21"/>
@@ -1795,29 +1780,29 @@
       <c r="J4" s="21"/>
       <c r="K4" s="21"/>
       <c r="L4" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M4" s="21"/>
       <c r="N4" s="21"/>
     </row>
-    <row r="5" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
@@ -1825,29 +1810,29 @@
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
       <c r="L5" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="21"/>
     </row>
-    <row r="6" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
@@ -1855,139 +1840,139 @@
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
       <c r="L6" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M6" s="21"/>
       <c r="N6" s="21"/>
     </row>
-    <row r="7" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>99</v>
-      </c>
       <c r="D7" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J7" s="21"/>
       <c r="K7" s="21"/>
       <c r="L7" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M7" s="21"/>
       <c r="N7" s="21"/>
     </row>
-    <row r="8" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="N8" s="21"/>
+    </row>
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="N8" s="21"/>
-    </row>
-    <row r="9" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>102</v>
-      </c>
       <c r="C9" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G9" s="21"/>
       <c r="H9" s="21"/>
       <c r="I9" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J9" s="21"/>
       <c r="K9" s="21"/>
       <c r="L9" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M9" s="21"/>
       <c r="N9" s="21"/>
     </row>
-    <row r="10" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G10" s="21"/>
       <c r="H10" s="21"/>
@@ -1995,29 +1980,29 @@
       <c r="J10" s="21"/>
       <c r="K10" s="21"/>
       <c r="L10" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M10" s="21"/>
       <c r="N10" s="21"/>
     </row>
-    <row r="11" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G11" s="21"/>
       <c r="H11" s="21"/>
@@ -2025,23 +2010,23 @@
       <c r="J11" s="21"/>
       <c r="K11" s="21"/>
       <c r="L11" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M11" s="21"/>
       <c r="N11" s="21"/>
     </row>
-    <row r="12" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E12" s="21"/>
       <c r="F12" s="21"/>
@@ -2051,29 +2036,29 @@
       <c r="J12" s="21"/>
       <c r="K12" s="21"/>
       <c r="L12" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M12" s="21"/>
       <c r="N12" s="21"/>
     </row>
-    <row r="13" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
@@ -2081,29 +2066,29 @@
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
       <c r="L13" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M13" s="21"/>
       <c r="N13" s="21"/>
     </row>
-    <row r="14" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G14" s="21"/>
       <c r="H14" s="21"/>
@@ -2111,23 +2096,23 @@
       <c r="J14" s="21"/>
       <c r="K14" s="21"/>
       <c r="L14" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M14" s="21"/>
       <c r="N14" s="21"/>
     </row>
-    <row r="15" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15" s="21"/>
@@ -2137,61 +2122,61 @@
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
       <c r="L15" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M15" s="21"/>
       <c r="N15" s="21"/>
     </row>
-    <row r="16" spans="1:30" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G16" s="21"/>
       <c r="H16" s="21"/>
       <c r="I16" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J16" s="21"/>
       <c r="K16" s="21"/>
       <c r="L16" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M16" s="21"/>
       <c r="N16" s="21"/>
     </row>
     <row r="17" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
@@ -2199,23 +2184,23 @@
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
       <c r="L17" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M17" s="21"/>
       <c r="N17" s="21"/>
     </row>
     <row r="18" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18" s="21"/>
@@ -2225,29 +2210,29 @@
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M18" s="21"/>
       <c r="N18" s="21"/>
     </row>
     <row r="19" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
@@ -2255,26 +2240,26 @@
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
       <c r="L19" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M19" s="21"/>
       <c r="N19" s="21"/>
     </row>
     <row r="20" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
@@ -2283,29 +2268,29 @@
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
       <c r="L20" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M20" s="21"/>
       <c r="N20" s="21"/>
     </row>
     <row r="21" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -2313,1917 +2298,1917 @@
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
       <c r="L21" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
     </row>
     <row r="22" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21"/>
       <c r="L22" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M22" s="21"/>
       <c r="N22" s="21"/>
     </row>
     <row r="23" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J23" s="21"/>
       <c r="K23" s="21"/>
       <c r="L23" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M23" s="21"/>
       <c r="N23" s="21"/>
     </row>
     <row r="24" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H24" s="21"/>
       <c r="I24" s="21"/>
       <c r="J24" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K24" s="21"/>
       <c r="L24" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M24" s="21"/>
       <c r="N24" s="21"/>
     </row>
     <row r="25" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C25" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H25" s="21"/>
       <c r="I25" s="21"/>
       <c r="J25" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K25" s="21"/>
       <c r="L25" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M25" s="21"/>
       <c r="N25" s="21"/>
     </row>
     <row r="26" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M26" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N26" s="21"/>
     </row>
     <row r="27" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C27" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H27" s="21"/>
       <c r="I27" s="21"/>
       <c r="J27" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M27" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N27" s="21"/>
     </row>
     <row r="28" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I28" s="21"/>
       <c r="J28" s="21"/>
       <c r="K28" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L28" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M28" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N28" s="21"/>
     </row>
     <row r="29" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C29" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I29" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L29" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="J29" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M29" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N29" s="21"/>
     </row>
     <row r="30" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I30" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M30" s="21"/>
       <c r="N30" s="21"/>
     </row>
     <row r="31" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I31" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
     </row>
     <row r="32" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I32" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
       <c r="L32" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
     </row>
     <row r="33" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J33" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K33" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L33" s="21"/>
       <c r="M33" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N33" s="21"/>
     </row>
     <row r="34" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I34" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K34" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L34" s="21"/>
       <c r="M34" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N34" s="21"/>
     </row>
     <row r="35" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J35" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K35" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L35" s="21"/>
       <c r="M35" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N35" s="21"/>
     </row>
     <row r="36" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K36" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L36" s="21"/>
       <c r="M36" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N36" s="21"/>
     </row>
     <row r="37" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J37" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K37" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L37" s="21"/>
       <c r="M37" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N37" s="21"/>
     </row>
     <row r="38" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F38" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I38" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K38" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L38" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="J38" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K38" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L38" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M38" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N38" s="21"/>
     </row>
     <row r="39" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J39" s="21"/>
       <c r="K39" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L39" s="21"/>
       <c r="M39" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N39" s="21"/>
     </row>
     <row r="40" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F40" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I40" s="21"/>
       <c r="J40" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K40" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L40" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M40" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N40" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J41" s="21"/>
       <c r="K41" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L41" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M41" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N41" s="21"/>
     </row>
     <row r="42" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
       <c r="I42" s="21"/>
       <c r="J42" s="21"/>
       <c r="K42" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L42" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M42" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N42" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J43" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K43" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L43" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M43" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N43" s="21"/>
     </row>
     <row r="44" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G44" s="21"/>
       <c r="H44" s="21"/>
       <c r="I44" s="21"/>
       <c r="J44" s="21"/>
       <c r="K44" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L44" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M44" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N44" s="21"/>
     </row>
     <row r="45" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C45" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I45" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J45" s="21"/>
       <c r="K45" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L45" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M45" s="21"/>
       <c r="N45" s="21"/>
     </row>
     <row r="46" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
       <c r="L46" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M46" s="21"/>
       <c r="N46" s="21"/>
     </row>
     <row r="47" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C47" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I47" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J47" s="21"/>
       <c r="K47" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L47" s="21"/>
       <c r="M47" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N47" s="21"/>
     </row>
     <row r="48" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J48" s="21"/>
       <c r="K48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L48" s="21"/>
       <c r="M48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N48" s="21"/>
     </row>
     <row r="49" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E49" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L49" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I49" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="J49" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="K49" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="L49" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M49" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N49" s="21"/>
     </row>
     <row r="50" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J50" s="21"/>
       <c r="K50" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L50" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M50" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N50" s="21"/>
     </row>
     <row r="51" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J51" s="21"/>
       <c r="K51" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L51" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="L51" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M51" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N51" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G52" s="21"/>
       <c r="H52" s="21"/>
       <c r="I52" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
       <c r="L52" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M52" s="21"/>
       <c r="N52" s="21"/>
     </row>
     <row r="53" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C53" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G53" s="21"/>
       <c r="H53" s="21"/>
       <c r="I53" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
       <c r="L53" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M53" s="21"/>
       <c r="N53" s="21"/>
     </row>
     <row r="54" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F54" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I54" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J54" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K54" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L54" s="21"/>
       <c r="M54" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N54" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G55" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I55" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J55" s="21"/>
       <c r="K55" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L55" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="L55" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M55" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N55" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E56" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F56" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G56" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H56" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J56" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L56" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="F56" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="G56" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J56" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K56" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L56" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M56" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N56" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C57" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F57" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I57" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="J57" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="K57" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="L57" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="G57" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J57" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="K57" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="L57" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M57" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N57" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F58" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G58" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I58" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J58" s="21"/>
       <c r="K58" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L58" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M58" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N58" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H59" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I59" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J59" s="21"/>
       <c r="K59" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L59" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="L59" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M59" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N59" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I60" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J60" s="21"/>
       <c r="K60" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L60" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="L60" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M60" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N60" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H61" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J61" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K61" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L61" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M61" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N61" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G62" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J62" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K62" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L62" s="22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M62" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N62" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L63" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N63" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L64" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M64" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N64" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F65" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G65" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L65" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="G65" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="H65" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="I65" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="J65" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="K65" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="L65" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M65" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N65" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G66" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I66" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J66" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="K66" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="L66" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H66" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="I66" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="J66" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="K66" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="L66" s="22" t="s">
-        <v>91</v>
-      </c>
       <c r="M66" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N66" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="33" t="s">
+      <c r="A69" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="33"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
-      <c r="M69" s="33"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
     </row>
     <row r="70" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="41" t="s">
+      <c r="B70" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
-      <c r="L70" s="42"/>
-      <c r="M70" s="43"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="41"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="41"/>
+      <c r="K70" s="41"/>
+      <c r="L70" s="41"/>
+      <c r="M70" s="42"/>
     </row>
     <row r="71" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B71" s="31" t="s">
+      <c r="B71" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="32"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="30"/>
     </row>
     <row r="72" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="44" t="s">
+      <c r="B72" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
-      <c r="H72" s="45"/>
-      <c r="I72" s="45"/>
-      <c r="J72" s="45"/>
-      <c r="K72" s="45"/>
-      <c r="L72" s="45"/>
-      <c r="M72" s="46"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
+      <c r="K72" s="44"/>
+      <c r="L72" s="44"/>
+      <c r="M72" s="45"/>
     </row>
     <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B73" s="47" t="s">
+      <c r="B73" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C73" s="48"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="48"/>
-      <c r="L73" s="48"/>
-      <c r="M73" s="49"/>
+      <c r="C73" s="47"/>
+      <c r="D73" s="47"/>
+      <c r="E73" s="47"/>
+      <c r="F73" s="47"/>
+      <c r="G73" s="47"/>
+      <c r="H73" s="47"/>
+      <c r="I73" s="47"/>
+      <c r="J73" s="47"/>
+      <c r="K73" s="47"/>
+      <c r="L73" s="47"/>
+      <c r="M73" s="48"/>
     </row>
     <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B74" s="38" t="s">
+      <c r="B74" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="39"/>
-      <c r="H74" s="39"/>
-      <c r="I74" s="39"/>
-      <c r="J74" s="39"/>
-      <c r="K74" s="39"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="40"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
+      <c r="L74" s="38"/>
+      <c r="M74" s="39"/>
     </row>
     <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B75" s="35" t="s">
+      <c r="B75" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="36"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="36"/>
-      <c r="I75" s="36"/>
-      <c r="J75" s="36"/>
-      <c r="K75" s="36"/>
-      <c r="L75" s="36"/>
-      <c r="M75" s="37"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="35"/>
+      <c r="M75" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4259,24 +4244,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+    </row>
+    <row r="2" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-    </row>
-    <row r="2" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="1:13" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
@@ -4300,19 +4285,19 @@
     </row>
     <row r="4" spans="1:13" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="F4" s="9">
         <v>1</v>
@@ -4320,19 +4305,19 @@
     </row>
     <row r="5" spans="1:13" ht="54.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="F5" s="11">
         <v>1</v>
@@ -4340,19 +4325,19 @@
     </row>
     <row r="6" spans="1:13" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="F6" s="9">
         <v>1</v>
@@ -4360,19 +4345,19 @@
     </row>
     <row r="7" spans="1:13" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="F7" s="11">
         <v>2</v>
@@ -4380,19 +4365,19 @@
     </row>
     <row r="8" spans="1:13" ht="99.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>83</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>84</v>
       </c>
       <c r="F8" s="9">
         <v>2</v>
@@ -4400,19 +4385,19 @@
     </row>
     <row r="9" spans="1:13" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>55</v>
       </c>
       <c r="F9" s="11">
         <v>1</v>
@@ -4420,19 +4405,19 @@
     </row>
     <row r="10" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>75</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="F10" s="13">
         <v>1</v>
@@ -4446,19 +4431,19 @@
     </row>
     <row r="11" spans="1:13" ht="73.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="F11" s="11">
         <v>1</v>
@@ -4467,19 +4452,19 @@
     </row>
     <row r="12" spans="1:13" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C12" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="15" t="s">
         <v>62</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>63</v>
       </c>
       <c r="F12" s="15">
         <v>1</v>
@@ -4487,19 +4472,19 @@
     </row>
     <row r="13" spans="1:13" ht="85.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>78</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="F13" s="16">
         <v>1</v>
@@ -4507,44 +4492,44 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
